--- a/test/expenses.xlsx
+++ b/test/expenses.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abhiraj Das\Documents\DMSBackend\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DC9C132E-9B06-4076-9FFB-75A8B6189316}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C0775BB-91AB-4D23-9652-99E8D43E32FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -286,12 +286,6 @@
     <t>GST789012</t>
   </si>
   <si>
-    <t>PAN1234567</t>
-  </si>
-  <si>
-    <t>PAN2345678</t>
-  </si>
-  <si>
     <t>PAN3456789</t>
   </si>
   <si>
@@ -511,9 +505,6 @@
     <t>SEZ</t>
   </si>
   <si>
-    <t>mumbai</t>
-  </si>
-  <si>
     <t>Branch B</t>
   </si>
   <si>
@@ -563,6 +554,15 @@
   </si>
   <si>
     <t>RIDER HELMET</t>
+  </si>
+  <si>
+    <t>Mumbai</t>
+  </si>
+  <si>
+    <t>sdfg</t>
+  </si>
+  <si>
+    <t>ASDFG7412A</t>
   </si>
 </sst>
 </file>
@@ -986,7 +986,7 @@
         <v>14</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>15</v>
@@ -1051,25 +1051,25 @@
     </row>
     <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="B2" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C2">
         <v>11111111111</v>
       </c>
       <c r="D2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E2" t="s">
+        <v>169</v>
+      </c>
+      <c r="F2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G2" t="s">
         <v>171</v>
-      </c>
-      <c r="E2" t="s">
-        <v>172</v>
-      </c>
-      <c r="F2" t="s">
-        <v>173</v>
-      </c>
-      <c r="G2" t="s">
-        <v>174</v>
       </c>
       <c r="H2" s="2">
         <v>43961</v>
@@ -1081,22 +1081,22 @@
         <v>37387</v>
       </c>
       <c r="K2" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="L2" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="M2" t="s">
         <v>75</v>
       </c>
       <c r="N2" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="O2" t="s">
-        <v>88</v>
+        <v>179</v>
       </c>
       <c r="P2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="Q2">
         <v>1</v>
@@ -1108,52 +1108,52 @@
         <v>0</v>
       </c>
       <c r="T2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="U2" t="s">
         <v>42</v>
       </c>
       <c r="V2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="W2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="X2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="Y2">
         <v>1200</v>
       </c>
       <c r="Z2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="AA2">
         <v>18</v>
       </c>
       <c r="AB2" t="s">
+        <v>131</v>
+      </c>
+      <c r="AC2" t="s">
         <v>133</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>135</v>
       </c>
       <c r="AD2">
         <v>6</v>
       </c>
       <c r="AE2" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="AF2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="AG2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="AH2">
         <v>1500</v>
       </c>
       <c r="AI2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AJ2">
         <v>18</v>
@@ -1161,7 +1161,7 @@
     </row>
     <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="B3" t="s">
         <v>37</v>
@@ -1191,10 +1191,10 @@
         <v>37388</v>
       </c>
       <c r="K3" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="L3" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="M3" t="s">
         <v>76</v>
@@ -1203,10 +1203,10 @@
         <v>82</v>
       </c>
       <c r="O3" t="s">
-        <v>89</v>
+        <v>180</v>
       </c>
       <c r="P3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="Q3">
         <v>1</v>
@@ -1218,52 +1218,52 @@
         <v>1</v>
       </c>
       <c r="T3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
       </c>
       <c r="V3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="W3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="X3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Y3">
         <v>1234</v>
       </c>
       <c r="Z3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="AA3">
         <v>18</v>
       </c>
       <c r="AB3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="AC3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AD3">
         <v>5</v>
       </c>
       <c r="AE3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AF3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="AG3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="AH3">
         <v>800</v>
       </c>
       <c r="AI3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="AJ3">
         <v>18</v>
@@ -1301,10 +1301,10 @@
         <v>37420</v>
       </c>
       <c r="K4" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="L4" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="M4" t="s">
         <v>77</v>
@@ -1313,10 +1313,10 @@
         <v>83</v>
       </c>
       <c r="O4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="Q4">
         <v>1</v>
@@ -1328,52 +1328,52 @@
         <v>0</v>
       </c>
       <c r="T4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
       </c>
       <c r="V4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="W4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="X4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="Y4">
         <v>1300</v>
       </c>
       <c r="Z4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="AA4">
         <v>18</v>
       </c>
       <c r="AB4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="AC4" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="AD4">
         <v>8</v>
       </c>
       <c r="AE4" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AF4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="AG4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="AH4">
         <v>1000</v>
       </c>
       <c r="AI4" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AJ4">
         <v>18</v>
@@ -1381,10 +1381,10 @@
     </row>
     <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B5" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C5" t="s">
         <v>45</v>
@@ -1411,10 +1411,10 @@
         <v>37360</v>
       </c>
       <c r="K5" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="L5" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="M5" t="s">
         <v>78</v>
@@ -1423,10 +1423,10 @@
         <v>84</v>
       </c>
       <c r="O5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="Q5">
         <v>1</v>
@@ -1438,52 +1438,52 @@
         <v>1</v>
       </c>
       <c r="T5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
       </c>
       <c r="V5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="W5" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="X5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="Y5">
         <v>2300</v>
       </c>
       <c r="Z5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="AA5">
         <v>18</v>
       </c>
       <c r="AB5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AC5" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="AD5">
         <v>34</v>
       </c>
       <c r="AE5" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AF5" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="AG5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="AH5">
         <v>1700</v>
       </c>
       <c r="AI5" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="AJ5">
         <v>18</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B6" t="s">
         <v>39</v>
@@ -1521,10 +1521,10 @@
         <v>44635</v>
       </c>
       <c r="K6" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="L6" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="M6" t="s">
         <v>79</v>
@@ -1533,10 +1533,10 @@
         <v>85</v>
       </c>
       <c r="O6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Q6">
         <v>1</v>
@@ -1548,52 +1548,52 @@
         <v>0</v>
       </c>
       <c r="T6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="U6" t="s">
         <v>46</v>
       </c>
       <c r="V6" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="W6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="X6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="Y6">
         <v>300</v>
       </c>
       <c r="Z6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="AA6">
         <v>18</v>
       </c>
       <c r="AB6" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="AC6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AD6">
         <v>8</v>
       </c>
       <c r="AE6" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="AF6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AG6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="AH6">
         <v>1600</v>
       </c>
       <c r="AI6" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="AJ6">
         <v>18</v>
@@ -1631,10 +1631,10 @@
         <v>37392</v>
       </c>
       <c r="K7" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="L7" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="M7" t="s">
         <v>80</v>
@@ -1643,10 +1643,10 @@
         <v>86</v>
       </c>
       <c r="O7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="Q7">
         <v>1</v>
@@ -1658,52 +1658,52 @@
         <v>1</v>
       </c>
       <c r="T7" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
       </c>
       <c r="V7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W7" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="X7" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="Y7">
         <v>500</v>
       </c>
       <c r="Z7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="AA7">
         <v>18</v>
       </c>
       <c r="AB7" t="s">
+        <v>132</v>
+      </c>
+      <c r="AC7" t="s">
         <v>134</v>
-      </c>
-      <c r="AC7" t="s">
-        <v>136</v>
       </c>
       <c r="AD7">
         <v>18</v>
       </c>
       <c r="AE7" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AF7" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="AG7" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="AH7">
         <v>2400</v>
       </c>
       <c r="AI7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="AJ7">
         <v>18</v>
@@ -1711,7 +1711,7 @@
     </row>
     <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B8" t="s">
         <v>41</v>
@@ -1741,10 +1741,10 @@
         <v>45521</v>
       </c>
       <c r="K8" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="L8" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="M8" t="s">
         <v>81</v>
@@ -1753,10 +1753,10 @@
         <v>87</v>
       </c>
       <c r="O8" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="P8" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="Q8">
         <v>1</v>
@@ -1768,52 +1768,52 @@
         <v>0</v>
       </c>
       <c r="T8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="U8" t="s">
         <v>48</v>
       </c>
       <c r="V8" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="W8" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="X8" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="Y8">
         <v>700</v>
       </c>
       <c r="Z8" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="AA8">
         <v>18</v>
       </c>
       <c r="AB8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="AC8" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AD8">
         <v>9</v>
       </c>
       <c r="AE8" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AF8" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="AG8" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="AH8">
         <v>2500</v>
       </c>
       <c r="AI8" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="AJ8">
         <v>18</v>
